--- a/data/trending_integrated_20261016_12.xlsx
+++ b/data/trending_integrated_20261016_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8810</v>
+        <v>8650</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.22%</t>
+          <t>'+20.98%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F2" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G2" t="n">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -610,7 +610,7 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>172994058820</v>
+        <v>176105454600</v>
       </c>
       <c r="P2" t="n">
         <v>8970</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>인수합병 관련 기대감과 코스닥 편입 이슈로 인한 급등이 예상됩니다. 텐버거 가능성에 대한 언급이 있으며, 투자 주의 종목 지정 가능성도 있습니다.</t>
+          <t>합병 가능성 및 텐버거 가능성에 대한 기대감이 있으나, 거래량 대비 주가 상승폭이 제한적이라는 의견도 존재함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['인수합병', '코스닥 편입', '텐버거']</t>
+          <t>['인수합병', '텐버거', '거래량']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7890</v>
+        <v>7820</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.09%</t>
+          <t>'+19.03%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>68112661795</v>
+        <v>68330947950</v>
       </c>
       <c r="P3" t="n">
         <v>10300</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>군공항 이전 이슈와 정치 테마 관련 기대감이 형성되고 있습니다. 신고가 돌파 시 추가 상승 가능성이 언급되며, 호남 관련주로도 주목받고 있습니다.</t>
+          <t>군공항 이전 관련 호재와 함께 단기 급등 가능성에 대한 기대감이 나타남. 투기과열종목 지정에 대한 언급도 포함됨.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['군공항 이전', '정치 테마', '신고가']</t>
+          <t>['군공항 이전', '단기 급등', '투기과열종목']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8280</v>
+        <v>8270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.80%</t>
+          <t>'+15.66%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F4" t="n">
         <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>46320266445</v>
+        <v>46694708620</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9570</v>
+        <v>9530</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.26%</t>
+          <t>'+7.81%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>81467871220</v>
+        <v>81715176620</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -931,123 +931,123 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18270</v>
+        <v>10360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.58%</t>
+          <t>'+4.33%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="G6" t="n">
-        <v>318</v>
+        <v>131</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17470</v>
+        <v>9930</v>
       </c>
       <c r="K6" t="n">
-        <v>18710</v>
+        <v>10100</v>
       </c>
       <c r="L6" t="n">
-        <v>20300</v>
+        <v>11100</v>
       </c>
       <c r="M6" t="n">
-        <v>17630</v>
+        <v>9860</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>140946375255</v>
+        <v>30774091645</v>
       </c>
       <c r="P6" t="n">
-        <v>28800</v>
+        <v>19380</v>
       </c>
       <c r="Q6" t="n">
-        <v>15780</v>
+        <v>3200</v>
       </c>
       <c r="R6" t="n">
-        <v>3000</v>
+        <v>-140000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>반도체 테마와 공급망 확충 수혜주로 언급되며, 글로벌 파운드리 연내 착공 관련 호재가 있습니다. 단일 계좌 투자 주의 종목 지정 가능성도 제기됩니다.</t>
+          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체 테마', '공급망', '파운드리']</t>
+          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18920</v>
+        <v>66000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.13%</t>
+          <t>'+4.27%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>144</v>
+        <v>389</v>
       </c>
       <c r="H7" t="n">
-        <v>27.77</v>
+        <v>22.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18170</v>
+        <v>63300</v>
       </c>
       <c r="K7" t="n">
-        <v>18340</v>
+        <v>63900</v>
       </c>
       <c r="L7" t="n">
-        <v>18990</v>
+        <v>66000</v>
       </c>
       <c r="M7" t="n">
-        <v>18110</v>
+        <v>63500</v>
       </c>
       <c r="N7" t="n">
-        <v>27.82</v>
+        <v>22.11</v>
       </c>
       <c r="O7" t="n">
-        <v>31117920640</v>
+        <v>84989996900</v>
       </c>
       <c r="P7" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q7" t="n">
-        <v>17210</v>
+        <v>57000</v>
       </c>
       <c r="R7" t="n">
-        <v>312000</v>
+        <v>50000</v>
       </c>
       <c r="S7" t="n">
-        <v>106000</v>
+        <v>-24000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
+          <t>원전 관련 긍정적 전망과 함께 3분기 매출 하회에 대한 실망감이 나타남. 주주 환원 정책 요구도 포함됨.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
+          <t>['원전', '매출 하회', '주주 환원']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10320</v>
+        <v>18930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.93%</t>
+          <t>'+4.18%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>27.77</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9930</v>
+        <v>18170</v>
       </c>
       <c r="K8" t="n">
-        <v>10100</v>
+        <v>18340</v>
       </c>
       <c r="L8" t="n">
-        <v>11100</v>
+        <v>18990</v>
       </c>
       <c r="M8" t="n">
-        <v>9860</v>
+        <v>18110</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>27.82</v>
       </c>
       <c r="O8" t="n">
-        <v>30671011375</v>
+        <v>31795966725</v>
       </c>
       <c r="P8" t="n">
-        <v>19380</v>
+        <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>3200</v>
+        <v>17210</v>
       </c>
       <c r="R8" t="n">
-        <v>-140000</v>
+        <v>312000</v>
       </c>
       <c r="S8" t="n">
-        <v>-3000</v>
+        <v>106000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
+          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
+          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65600</v>
+        <v>18160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.63%</t>
+          <t>'+3.95%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="F9" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="G9" t="n">
-        <v>377</v>
+        <v>334</v>
       </c>
       <c r="H9" t="n">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>63300</v>
+        <v>17470</v>
       </c>
       <c r="K9" t="n">
-        <v>63900</v>
+        <v>18710</v>
       </c>
       <c r="L9" t="n">
-        <v>65800</v>
+        <v>20300</v>
       </c>
       <c r="M9" t="n">
-        <v>63500</v>
+        <v>17630</v>
       </c>
       <c r="N9" t="n">
-        <v>22.11</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>82839842550</v>
+        <v>142665417855</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>28800</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>15780</v>
       </c>
       <c r="R9" t="n">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="S9" t="n">
-        <v>-24000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>원전 관련 긍정적 뉴스에도 불구하고 주가 흐름이 부진하며, 외국계 증권사의 매도 움직임이 관찰됩니다. 신뢰도 저하에 대한 우려도 제기됩니다.</t>
+          <t>반도체 테마 관련 수혜주로 언급되며 글로벌 파운드리 공장 착공 소식이 호재로 작용할 가능성이 제시됨. 단일 계좌 투기 과열 종목 지정에 대한 우려도 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전 르네상스', '외인 매도', '신뢰도']</t>
+          <t>['반도체', '파운드리', '단일 계좌']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23850</v>
+        <v>216500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.80%</t>
+          <t>'+3.10%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.02</v>
+        <v>-0.18</v>
       </c>
       <c r="E10" t="n">
-        <v>56</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>501</v>
       </c>
       <c r="G10" t="n">
-        <v>319</v>
+        <v>1062</v>
       </c>
       <c r="H10" t="n">
-        <v>9.23</v>
+        <v>45.98</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>23200</v>
+        <v>210000</v>
       </c>
       <c r="K10" t="n">
-        <v>23250</v>
+        <v>215000</v>
       </c>
       <c r="L10" t="n">
-        <v>24250</v>
+        <v>217500</v>
       </c>
       <c r="M10" t="n">
-        <v>22900</v>
+        <v>210500</v>
       </c>
       <c r="N10" t="n">
-        <v>9.210000000000001</v>
+        <v>46.16</v>
       </c>
       <c r="O10" t="n">
-        <v>33735111250</v>
+        <v>1862411545750</v>
       </c>
       <c r="P10" t="n">
-        <v>24950</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>17910</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>435000</v>
+        <v>-684000</v>
       </c>
       <c r="S10" t="n">
-        <v>-20000</v>
+        <v>-108000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
+          <t>정치적 이슈에 대한 불만과 함께 주주 손실에 대한 우려가 제기됨. 외인 매매 동향 및 유가 변동성에 대한 언급도 포함됨.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['운항수익', '영업이익', 'SCFI']</t>
+          <t>['주주 손실', '외인 매매', '유가 변동성']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>215500</v>
+        <v>23900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.62%</t>
+          <t>'+3.02%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.18</v>
+        <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>57</v>
       </c>
       <c r="F11" t="n">
-        <v>496</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>1070</v>
+        <v>331</v>
       </c>
       <c r="H11" t="n">
-        <v>45.98</v>
+        <v>9.23</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,139 +1423,139 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>210000</v>
+        <v>23200</v>
       </c>
       <c r="K11" t="n">
-        <v>215000</v>
+        <v>23250</v>
       </c>
       <c r="L11" t="n">
-        <v>217500</v>
+        <v>24250</v>
       </c>
       <c r="M11" t="n">
-        <v>210500</v>
+        <v>22900</v>
       </c>
       <c r="N11" t="n">
-        <v>46.16</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>1813294169750</v>
+        <v>34388022700</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>24950</v>
       </c>
       <c r="Q11" t="n">
-        <v>94500</v>
+        <v>17910</v>
       </c>
       <c r="R11" t="n">
-        <v>-684000</v>
+        <v>435000</v>
       </c>
       <c r="S11" t="n">
-        <v>-108000</v>
+        <v>-20000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 노조 관련 언급이 많으며, 주가 하락 및 외인 매도에 대한 부정적 인식이 나타납니다. AI 관련 긍정적 언급도 일부 있습니다.</t>
+          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['외인 매도', '정치 이슈', 'AI']</t>
+          <t>['운항수익', '영업이익', 'SCFI']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>011200</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13400</v>
+        <v>15090</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.60%</t>
+          <t>'+2.86%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>184</v>
+        <v>325</v>
       </c>
       <c r="H12" t="n">
-        <v>3.42</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13060</v>
+        <v>14670</v>
       </c>
       <c r="K12" t="n">
-        <v>13390</v>
+        <v>14800</v>
       </c>
       <c r="L12" t="n">
-        <v>13620</v>
+        <v>15270</v>
       </c>
       <c r="M12" t="n">
-        <v>12910</v>
+        <v>14800</v>
       </c>
       <c r="N12" t="n">
-        <v>3.21</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>35005857025</v>
+        <v>25241163120</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>1640</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-62000</v>
+        <v>-92000</v>
       </c>
       <c r="S12" t="n">
-        <v>-11000</v>
+        <v>7000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
+          <t>대형 수주 계약 체결 및 목표가 상향 조정에 대한 긍정적 전망이 제시됨. 주가 조작 의혹 및 금감원 점검 등 부정적 언급도 혼재됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '미국장 반등']</t>
+          <t>['대형 수주', '목표가 상향', '주가 조작']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,91 +1563,91 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1292000</v>
+        <v>13430</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.38%</t>
+          <t>'+2.83%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>512</v>
+        <v>30</v>
       </c>
       <c r="G13" t="n">
-        <v>1173</v>
+        <v>184</v>
       </c>
       <c r="H13" t="n">
-        <v>48.85</v>
+        <v>3.42</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1262000</v>
+        <v>13060</v>
       </c>
       <c r="K13" t="n">
-        <v>1290000</v>
+        <v>13390</v>
       </c>
       <c r="L13" t="n">
-        <v>1308000</v>
+        <v>13620</v>
       </c>
       <c r="M13" t="n">
-        <v>1247000</v>
+        <v>12910</v>
       </c>
       <c r="N13" t="n">
-        <v>49.02</v>
+        <v>3.21</v>
       </c>
       <c r="O13" t="n">
-        <v>3015016395500</v>
+        <v>35260746355</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>420500</v>
+        <v>1640</v>
       </c>
       <c r="R13" t="n">
-        <v>-448000</v>
+        <v>-62000</v>
       </c>
       <c r="S13" t="n">
-        <v>-27000</v>
+        <v>-11000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외국인 매도세와 주가 하락이 지속되며, 반등의 동력이 약하다는 분석이 나옵니다. 정치적 이슈와 관련된 언급도 혼재되어 있습니다.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외인 매도', '주가 하락', '정치 이슈']</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,95 +1655,95 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15010</v>
+        <v>41850</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.32%</t>
+          <t>'+2.70%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>136</v>
+        <v>223</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="G14" t="n">
-        <v>308</v>
+        <v>854</v>
       </c>
       <c r="H14" t="n">
-        <v>9.779999999999999</v>
+        <v>12.97</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14670</v>
+        <v>40750</v>
       </c>
       <c r="K14" t="n">
-        <v>14800</v>
+        <v>40600</v>
       </c>
       <c r="L14" t="n">
-        <v>15270</v>
+        <v>41950</v>
       </c>
       <c r="M14" t="n">
-        <v>14800</v>
+        <v>40050</v>
       </c>
       <c r="N14" t="n">
-        <v>9.710000000000001</v>
+        <v>12.84</v>
       </c>
       <c r="O14" t="n">
-        <v>24815590720</v>
+        <v>10347646125</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>69200</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>24150</v>
       </c>
       <c r="R14" t="n">
-        <v>-92000</v>
+        <v>15000</v>
       </c>
       <c r="S14" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대형 수주 계약 체결 및 목표가 상향 조정 공시가 확인되었습니다. 내년 건설주 상승 전망과 함께 긍정적인 분위기가 형성되고 있습니다.</t>
+          <t>FDA 승인 관련 기대감과 함께 IR 발표, 외국인 매수세 등 긍정적인 요소가 언급되나, 일부 불안감과 회의적인 시각도 존재함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['수주 공시', '목표가 상향', '건설주 전망']</t>
+          <t>['FDA 승인', 'IR 발표', '외인']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41625</v>
+        <v>1292000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.15%</t>
+          <t>'+2.38%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.13</v>
+        <v>-0.17</v>
       </c>
       <c r="E15" t="n">
-        <v>220</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>122</v>
+        <v>512</v>
       </c>
       <c r="G15" t="n">
-        <v>844</v>
+        <v>1233</v>
       </c>
       <c r="H15" t="n">
-        <v>12.97</v>
+        <v>48.85</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>40750</v>
+        <v>1262000</v>
       </c>
       <c r="K15" t="n">
-        <v>40600</v>
+        <v>1290000</v>
       </c>
       <c r="L15" t="n">
-        <v>41650</v>
+        <v>1308000</v>
       </c>
       <c r="M15" t="n">
-        <v>40050</v>
+        <v>1247000</v>
       </c>
       <c r="N15" t="n">
-        <v>12.84</v>
+        <v>49.02</v>
       </c>
       <c r="O15" t="n">
-        <v>9552531375</v>
+        <v>3077476486500</v>
       </c>
       <c r="P15" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>24150</v>
+        <v>420500</v>
       </c>
       <c r="R15" t="n">
-        <v>15000</v>
+        <v>-448000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-27000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>FDA 승인 관련 기대감과 함께 IR 발표, 외국인 매수세 등 긍정적인 요소가 언급되나, 일부 불안감과 회의적인 시각도 존재함.</t>
+          <t>정치적 상황과 외인 매도세로 인한 주가 하락에 대한 불만이 제기됨. 솔리다임 상장 관련 언급도 포함됨.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['FDA 승인', 'IR 발표', '외인']</t>
+          <t>['외인 매도', '주가 하락', '솔리다임']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14890</v>
+        <v>20950</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.33%</t>
+          <t>'+0.96%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="E16" t="n">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="F16" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H16" t="n">
-        <v>0.11</v>
+        <v>4.28</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14940</v>
+        <v>20750</v>
       </c>
       <c r="K16" t="n">
-        <v>14940</v>
+        <v>20500</v>
       </c>
       <c r="L16" t="n">
-        <v>16290</v>
+        <v>21500</v>
       </c>
       <c r="M16" t="n">
-        <v>14330</v>
+        <v>19440</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O16" t="n">
-        <v>39237157450</v>
+        <v>42280966745</v>
       </c>
       <c r="P16" t="n">
-        <v>30800</v>
+        <v>22450</v>
       </c>
       <c r="Q16" t="n">
-        <v>9810</v>
+        <v>6320</v>
       </c>
       <c r="R16" t="n">
-        <v>7000</v>
+        <v>28000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>상장 사기 의혹 및 과도한 공모가 논란이 제기되며, 주가 부양 후 개인 투자자에게 물량을 넘기는 듯한 움직임이 관찰됩니다. 자진 상폐 요구도 있습니다.</t>
+          <t>금융권 보안 투자 확대 및 신규 납품 요청 증가에 따른 긍정적 전망이 제시됨. 해킹 시도 증가로 인한 보안 강화 필요성이 언급됨.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['상장 사기', '공모가 논란', '자진 상폐']</t>
+          <t>['보안 투자', '납품 요청', '해킹']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20250</v>
+        <v>14810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.41%</t>
+          <t>'-0.87%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G17" t="n">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="H17" t="n">
-        <v>4.28</v>
+        <v>0.11</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,60 +1975,60 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>20750</v>
+        <v>14940</v>
       </c>
       <c r="K17" t="n">
-        <v>20500</v>
+        <v>14940</v>
       </c>
       <c r="L17" t="n">
-        <v>21500</v>
+        <v>16290</v>
       </c>
       <c r="M17" t="n">
-        <v>19440</v>
+        <v>14330</v>
       </c>
       <c r="N17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>35878935195</v>
+        <v>39593300830</v>
       </c>
       <c r="P17" t="n">
-        <v>22450</v>
+        <v>30800</v>
       </c>
       <c r="Q17" t="n">
-        <v>6320</v>
+        <v>9810</v>
       </c>
       <c r="R17" t="n">
-        <v>28000</v>
+        <v>7000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>농협, KDB 등 금융권 신규 납품 요청 및 보안 강화 트렌드 속 수혜 기대. 해킹 사고 증가 추세 및 프로그램 매매 관련 이슈.</t>
+          <t>상장 사기 및 지나치게 높은 공모가에 대한 강한 비판이 제기됨. 회사 경영진의 무능함과 자진 상폐 요구가 포함됨.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['보안', '신규 납품', '해킹 사고']</t>
+          <t>['상장 사기', '공모가', '자진 상폐']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27350</v>
+        <v>27300</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.13%</t>
+          <t>'-7.30%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F18" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G18" t="n">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="H18" t="n">
         <v>53.46</v>
@@ -2082,7 +2082,7 @@
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>101678704925</v>
+        <v>104429637875</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>

--- a/data/trending_integrated_20261016_12.xlsx
+++ b/data/trending_integrated_20261016_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8650</v>
+        <v>8730</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.98%</t>
+          <t>'+22.10%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F2" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G2" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -610,7 +610,7 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>176105454600</v>
+        <v>179329349100</v>
       </c>
       <c r="P2" t="n">
         <v>8970</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7820</v>
+        <v>7770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.03%</t>
+          <t>'+18.26%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>68330947950</v>
+        <v>68744668375</v>
       </c>
       <c r="P3" t="n">
         <v>10300</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>군공항 이전 관련 호재와 함께 단기 급등 가능성에 대한 기대감이 나타남. 투기과열종목 지정에 대한 언급도 포함됨.</t>
+          <t>군공항 이전 및 호남 반도체 관련 테마 언급. 투경 종목으로 급등 가능성 및 급락 주의 신호.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['군공항 이전', '단기 급등', '투기과열종목']</t>
+          <t>['군공항', '호남 반도체', '투경']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8270</v>
+        <v>8220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.66%</t>
+          <t>'+14.97%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F4" t="n">
         <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>46694708620</v>
+        <v>47568912125</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9530</v>
+        <v>9550</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.81%</t>
+          <t>'+8.03%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>81715176620</v>
+        <v>82468854730</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10360</v>
+        <v>10390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.33%</t>
+          <t>'+4.63%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>28</v>
       </c>
       <c r="G6" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>30774091645</v>
+        <v>30924781800</v>
       </c>
       <c r="P6" t="n">
         <v>19380</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66000</v>
+        <v>18960</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.27%</t>
+          <t>'+4.35%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="F7" t="n">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>389</v>
+        <v>158</v>
       </c>
       <c r="H7" t="n">
-        <v>22.1</v>
+        <v>27.77</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>63300</v>
+        <v>18170</v>
       </c>
       <c r="K7" t="n">
-        <v>63900</v>
+        <v>18340</v>
       </c>
       <c r="L7" t="n">
-        <v>66000</v>
+        <v>18990</v>
       </c>
       <c r="M7" t="n">
-        <v>63500</v>
+        <v>18110</v>
       </c>
       <c r="N7" t="n">
-        <v>22.11</v>
+        <v>27.82</v>
       </c>
       <c r="O7" t="n">
-        <v>84989996900</v>
+        <v>32625505945</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q7" t="n">
-        <v>57000</v>
+        <v>17210</v>
       </c>
       <c r="R7" t="n">
-        <v>50000</v>
+        <v>312000</v>
       </c>
       <c r="S7" t="n">
-        <v>-24000</v>
+        <v>106000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원전 관련 긍정적 전망과 함께 3분기 매출 하회에 대한 실망감이 나타남. 주주 환원 정책 요구도 포함됨.</t>
+          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '매출 하회', '주주 환원']</t>
+          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18930</v>
+        <v>65900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.18%</t>
+          <t>'+4.11%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>144</v>
+        <v>395</v>
       </c>
       <c r="H8" t="n">
-        <v>27.77</v>
+        <v>22.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,143 +1147,143 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18170</v>
+        <v>63300</v>
       </c>
       <c r="K8" t="n">
-        <v>18340</v>
+        <v>63900</v>
       </c>
       <c r="L8" t="n">
-        <v>18990</v>
+        <v>66200</v>
       </c>
       <c r="M8" t="n">
-        <v>18110</v>
+        <v>63500</v>
       </c>
       <c r="N8" t="n">
-        <v>27.82</v>
+        <v>22.11</v>
       </c>
       <c r="O8" t="n">
-        <v>31795966725</v>
+        <v>87579338150</v>
       </c>
       <c r="P8" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>17210</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>312000</v>
+        <v>50000</v>
       </c>
       <c r="S8" t="n">
-        <v>106000</v>
+        <v>-24000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
+          <t>원전 관련 긍정적 전망과 함께 3분기 매출 하회에 대한 실망감이 나타남. 주주 환원 정책 요구도 포함됨.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
+          <t>['원전', '매출 하회', '주주 환원']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18160</v>
+        <v>216500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.95%</t>
+          <t>'+3.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="E9" t="n">
-        <v>151</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>95</v>
+        <v>501</v>
       </c>
       <c r="G9" t="n">
-        <v>334</v>
+        <v>1122</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>45.98</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17470</v>
+        <v>210000</v>
       </c>
       <c r="K9" t="n">
-        <v>18710</v>
+        <v>215000</v>
       </c>
       <c r="L9" t="n">
-        <v>20300</v>
+        <v>217500</v>
       </c>
       <c r="M9" t="n">
-        <v>17630</v>
+        <v>210500</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>46.16</v>
       </c>
       <c r="O9" t="n">
-        <v>142665417855</v>
+        <v>1909123093750</v>
       </c>
       <c r="P9" t="n">
-        <v>28800</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>15780</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>3000</v>
+        <v>-684000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-108000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>반도체 테마 관련 수혜주로 언급되며 글로벌 파운드리 공장 착공 소식이 호재로 작용할 가능성이 제시됨. 단일 계좌 투기 과열 종목 지정에 대한 우려도 존재.</t>
+          <t>정치적 이슈 언급하며 주가 하락 전망. 외인/기관 매도세 지속.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '파운드리', '단일 계좌']</t>
+          <t>['이재명', '외인', '매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>216500</v>
+        <v>15120</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.10%</t>
+          <t>'+3.07%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>149</v>
       </c>
       <c r="F10" t="n">
-        <v>501</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>1062</v>
+        <v>335</v>
       </c>
       <c r="H10" t="n">
-        <v>45.98</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>210000</v>
+        <v>14670</v>
       </c>
       <c r="K10" t="n">
-        <v>215000</v>
+        <v>14800</v>
       </c>
       <c r="L10" t="n">
-        <v>217500</v>
+        <v>15270</v>
       </c>
       <c r="M10" t="n">
-        <v>210500</v>
+        <v>14800</v>
       </c>
       <c r="N10" t="n">
-        <v>46.16</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>1862411545750</v>
+        <v>25865339765</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-684000</v>
+        <v>-92000</v>
       </c>
       <c r="S10" t="n">
-        <v>-108000</v>
+        <v>7000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈에 대한 불만과 함께 주주 손실에 대한 우려가 제기됨. 외인 매매 동향 및 유가 변동성에 대한 언급도 포함됨.</t>
+          <t>단일판매ㆍ공급계약 공시 확인. 건설주 상승 전망 및 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주주 손실', '외인 매매', '유가 변동성']</t>
+          <t>['공시', '건설주', '수주']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1406,13 +1406,13 @@
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="H11" t="n">
         <v>9.23</v>
@@ -1438,7 +1438,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>34388022700</v>
+        <v>35057617100</v>
       </c>
       <c r="P11" t="n">
         <v>24950</v>
@@ -1483,79 +1483,79 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15090</v>
+        <v>13440</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.86%</t>
+          <t>'+2.91%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>143</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G12" t="n">
-        <v>325</v>
+        <v>184</v>
       </c>
       <c r="H12" t="n">
-        <v>9.779999999999999</v>
+        <v>3.42</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14670</v>
+        <v>13060</v>
       </c>
       <c r="K12" t="n">
-        <v>14800</v>
+        <v>13390</v>
       </c>
       <c r="L12" t="n">
-        <v>15270</v>
+        <v>13620</v>
       </c>
       <c r="M12" t="n">
-        <v>14800</v>
+        <v>12910</v>
       </c>
       <c r="N12" t="n">
-        <v>9.710000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="O12" t="n">
-        <v>25241163120</v>
+        <v>35837174325</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>1640</v>
       </c>
       <c r="R12" t="n">
-        <v>-92000</v>
+        <v>-62000</v>
       </c>
       <c r="S12" t="n">
-        <v>7000</v>
+        <v>-11000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대형 수주 계약 체결 및 목표가 상향 조정에 대한 긍정적 전망이 제시됨. 주가 조작 의혹 및 금감원 점검 등 부정적 언급도 혼재됨.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대형 수주', '목표가 상향', '주가 조작']</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,43 +1563,43 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13430</v>
+        <v>41900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.83%</t>
+          <t>'+2.82%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>229</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="G13" t="n">
-        <v>184</v>
+        <v>893</v>
       </c>
       <c r="H13" t="n">
-        <v>3.42</v>
+        <v>12.97</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,143 +1607,143 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13060</v>
+        <v>40750</v>
       </c>
       <c r="K13" t="n">
-        <v>13390</v>
+        <v>40600</v>
       </c>
       <c r="L13" t="n">
-        <v>13620</v>
+        <v>41950</v>
       </c>
       <c r="M13" t="n">
-        <v>12910</v>
+        <v>40050</v>
       </c>
       <c r="N13" t="n">
-        <v>3.21</v>
+        <v>12.84</v>
       </c>
       <c r="O13" t="n">
-        <v>35260746355</v>
+        <v>10501880275</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>69200</v>
       </c>
       <c r="Q13" t="n">
-        <v>1640</v>
+        <v>24150</v>
       </c>
       <c r="R13" t="n">
-        <v>-62000</v>
+        <v>15000</v>
       </c>
       <c r="S13" t="n">
-        <v>-11000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
+          <t>Class1 발표 및 FDA 승인 관련 기대감. 외인 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '미국장 반등']</t>
+          <t>['Class1', 'FDA', '외인']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>41850</v>
+        <v>1292000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.70%</t>
+          <t>'+2.38%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.13</v>
+        <v>-0.17</v>
       </c>
       <c r="E14" t="n">
-        <v>223</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>123</v>
+        <v>514</v>
       </c>
       <c r="G14" t="n">
-        <v>854</v>
+        <v>1280</v>
       </c>
       <c r="H14" t="n">
-        <v>12.97</v>
+        <v>48.85</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>40750</v>
+        <v>1262000</v>
       </c>
       <c r="K14" t="n">
-        <v>40600</v>
+        <v>1290000</v>
       </c>
       <c r="L14" t="n">
-        <v>41950</v>
+        <v>1308000</v>
       </c>
       <c r="M14" t="n">
-        <v>40050</v>
+        <v>1247000</v>
       </c>
       <c r="N14" t="n">
-        <v>12.84</v>
+        <v>49.02</v>
       </c>
       <c r="O14" t="n">
-        <v>10347646125</v>
+        <v>3125239441500</v>
       </c>
       <c r="P14" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>24150</v>
+        <v>420500</v>
       </c>
       <c r="R14" t="n">
-        <v>15000</v>
+        <v>-448000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-27000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>FDA 승인 관련 기대감과 함께 IR 발표, 외국인 매수세 등 긍정적인 요소가 언급되나, 일부 불안감과 회의적인 시각도 존재함.</t>
+          <t>정치적 상황과 연계하여 주가 하락 우려 제기. 외인 매도 지속 및 전저점 하회 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['FDA 승인', 'IR 발표', '외인']</t>
+          <t>['외인', '주가 하락', '정치']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1292000</v>
+        <v>17860</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.38%</t>
+          <t>'+2.23%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>154</v>
       </c>
       <c r="F15" t="n">
-        <v>512</v>
+        <v>95</v>
       </c>
       <c r="G15" t="n">
-        <v>1233</v>
+        <v>341</v>
       </c>
       <c r="H15" t="n">
-        <v>48.85</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1262000</v>
+        <v>17470</v>
       </c>
       <c r="K15" t="n">
-        <v>1290000</v>
+        <v>18710</v>
       </c>
       <c r="L15" t="n">
-        <v>1308000</v>
+        <v>20300</v>
       </c>
       <c r="M15" t="n">
-        <v>1247000</v>
+        <v>17630</v>
       </c>
       <c r="N15" t="n">
-        <v>49.02</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3077476486500</v>
+        <v>145153993130</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>28800</v>
       </c>
       <c r="Q15" t="n">
-        <v>420500</v>
+        <v>15780</v>
       </c>
       <c r="R15" t="n">
-        <v>-448000</v>
+        <v>3000</v>
       </c>
       <c r="S15" t="n">
-        <v>-27000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 상황과 외인 매도세로 인한 주가 하락에 대한 불만이 제기됨. 솔리다임 상장 관련 언급도 포함됨.</t>
+          <t>반도체 테마 및 글로벌 파운드리 연내 착공 뉴스 기반 상승 기대. 단일계좌 투주 종목으로 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['외인 매도', '주가 하락', '솔리다임']</t>
+          <t>['반도체', '파운드리', '단일계좌']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20950</v>
+        <v>21000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.96%</t>
+          <t>'+1.20%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2.5</v>
       </c>
       <c r="E16" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F16" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G16" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="H16" t="n">
         <v>4.28</v>
@@ -1898,7 +1898,7 @@
         <v>1.78</v>
       </c>
       <c r="O16" t="n">
-        <v>42280966745</v>
+        <v>46817577320</v>
       </c>
       <c r="P16" t="n">
         <v>22450</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>금융권 보안 투자 확대 및 신규 납품 요청 증가에 따른 긍정적 전망이 제시됨. 해킹 시도 증가로 인한 보안 강화 필요성이 언급됨.</t>
+          <t>금융권 해킹 이슈 및 보안 투자 확대 뉴스 기반 신규 납품 요청 쇄도. 연기금 매수세 확인.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['보안 투자', '납품 요청', '해킹']</t>
+          <t>['보안', '해킹', '신규 납품']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14810</v>
+        <v>14710</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.87%</t>
+          <t>'-1.54%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F17" t="n">
         <v>68</v>
       </c>
       <c r="G17" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H17" t="n">
         <v>0.11</v>
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>39593300830</v>
+        <v>39920806600</v>
       </c>
       <c r="P17" t="n">
         <v>30800</v>
@@ -2039,27 +2039,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27300</v>
+        <v>27000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.30%</t>
+          <t>'-8.32%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" t="n">
         <v>69</v>
       </c>
       <c r="G18" t="n">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="H18" t="n">
-        <v>53.46</v>
+        <v>53.41</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2076,13 +2076,13 @@
         <v>29600</v>
       </c>
       <c r="M18" t="n">
-        <v>27100</v>
+        <v>26950</v>
       </c>
       <c r="N18" t="n">
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>104429637875</v>
+        <v>115039405925</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>

--- a/data/trending_integrated_20261016_12.xlsx
+++ b/data/trending_integrated_20261016_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8730</v>
+        <v>8610</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.10%</t>
+          <t>'+20.42%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G2" t="n">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -610,7 +610,7 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>179329349100</v>
+        <v>183524176735</v>
       </c>
       <c r="P2" t="n">
         <v>8970</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>합병 가능성 및 텐버거 가능성에 대한 기대감이 있으나, 거래량 대비 주가 상승폭이 제한적이라는 의견도 존재함.</t>
+          <t>높은 상승률 기록. 인수합병 기대감 및 텐버거 가능성 언급. 거래량 증가 및 악성매물 소화 과정 설명.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7770</v>
+        <v>7710</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.26%</t>
+          <t>'+17.35%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>68744668375</v>
+        <v>69457162180</v>
       </c>
       <c r="P3" t="n">
         <v>10300</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8220</v>
+        <v>8200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.97%</t>
+          <t>'+14.69%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>47568912125</v>
+        <v>48410343615</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9550</v>
+        <v>9470</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.03%</t>
+          <t>'+7.13%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>82468854730</v>
+        <v>83478189095</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -931,92 +931,92 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10390</v>
+        <v>18270</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.63%</t>
+          <t>'+4.58%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="F6" t="n">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="G6" t="n">
-        <v>138</v>
+        <v>346</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9930</v>
+        <v>17470</v>
       </c>
       <c r="K6" t="n">
-        <v>10100</v>
+        <v>18710</v>
       </c>
       <c r="L6" t="n">
-        <v>11100</v>
+        <v>20300</v>
       </c>
       <c r="M6" t="n">
-        <v>9860</v>
+        <v>17630</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>30924781800</v>
+        <v>148927990820</v>
       </c>
       <c r="P6" t="n">
-        <v>19380</v>
+        <v>28800</v>
       </c>
       <c r="Q6" t="n">
-        <v>3200</v>
+        <v>15780</v>
       </c>
       <c r="R6" t="n">
-        <v>-140000</v>
+        <v>3000</v>
       </c>
       <c r="S6" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
+          <t>반도체 테마 및 글로벌 파운드리 연내 착공 뉴스 기반 상승 기대. 단일계좌 투주 종목으로 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
+          <t>['반도체', '파운드리', '단일계좌']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -1038,13 +1038,13 @@
         <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H7" t="n">
         <v>27.77</v>
@@ -1070,7 +1070,7 @@
         <v>27.82</v>
       </c>
       <c r="O7" t="n">
-        <v>32625505945</v>
+        <v>33348139755</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1130,13 +1130,13 @@
         <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="H8" t="n">
         <v>22.1</v>
@@ -1162,7 +1162,7 @@
         <v>22.11</v>
       </c>
       <c r="O8" t="n">
-        <v>87579338150</v>
+        <v>89547543000</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원전 관련 긍정적 전망과 함께 3분기 매출 하회에 대한 실망감이 나타남. 주주 환원 정책 요구도 포함됨.</t>
+          <t>원전 관련 긍정적 언급 및 뉴스케일파워 상승 마감 소식. 주주환원 정책 및 신뢰도에 대한 지적.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '매출 하회', '주주 환원']</t>
+          <t>['원전', '뉴스케일파워', '주주환원']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>216500</v>
+        <v>10330</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.10%</t>
+          <t>'+4.03%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>501</v>
+        <v>28</v>
       </c>
       <c r="G9" t="n">
-        <v>1122</v>
+        <v>138</v>
       </c>
       <c r="H9" t="n">
-        <v>45.98</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>210000</v>
+        <v>9930</v>
       </c>
       <c r="K9" t="n">
-        <v>215000</v>
+        <v>10100</v>
       </c>
       <c r="L9" t="n">
-        <v>217500</v>
+        <v>11100</v>
       </c>
       <c r="M9" t="n">
-        <v>210500</v>
+        <v>9860</v>
       </c>
       <c r="N9" t="n">
-        <v>46.16</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1909123093750</v>
+        <v>31052767705</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>3200</v>
       </c>
       <c r="R9" t="n">
-        <v>-684000</v>
+        <v>-140000</v>
       </c>
       <c r="S9" t="n">
-        <v>-108000</v>
+        <v>-3000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 이슈 언급하며 주가 하락 전망. 외인/기관 매도세 지속.</t>
+          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['이재명', '외인', '매도']</t>
+          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15120</v>
+        <v>216250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.07%</t>
+          <t>'+2.98%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.18</v>
       </c>
       <c r="E10" t="n">
-        <v>149</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>501</v>
       </c>
       <c r="G10" t="n">
-        <v>335</v>
+        <v>1174</v>
       </c>
       <c r="H10" t="n">
-        <v>9.779999999999999</v>
+        <v>45.98</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14670</v>
+        <v>210000</v>
       </c>
       <c r="K10" t="n">
-        <v>14800</v>
+        <v>215000</v>
       </c>
       <c r="L10" t="n">
-        <v>15270</v>
+        <v>217500</v>
       </c>
       <c r="M10" t="n">
-        <v>14800</v>
+        <v>210500</v>
       </c>
       <c r="N10" t="n">
-        <v>9.710000000000001</v>
+        <v>46.16</v>
       </c>
       <c r="O10" t="n">
-        <v>25865339765</v>
+        <v>1970457145250</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>-92000</v>
+        <v>-684000</v>
       </c>
       <c r="S10" t="n">
-        <v>7000</v>
+        <v>-108000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>단일판매ㆍ공급계약 공시 확인. 건설주 상승 전망 및 주가 조작 의혹 제기.</t>
+          <t>이재명 정부 및 민주당 관련 부정적 언급과 함께 외인/기관 매도세 포착. 애플의 중국산 반도체 사용 검토 뉴스 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공시', '건설주', '수주']</t>
+          <t>['역배열', '외인매도', '애플']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23900</v>
+        <v>23850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.02%</t>
+          <t>'+2.80%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
         <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="H11" t="n">
         <v>9.23</v>
@@ -1438,7 +1438,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>35057617100</v>
+        <v>35619989025</v>
       </c>
       <c r="P11" t="n">
         <v>24950</v>
@@ -1483,79 +1483,79 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13440</v>
+        <v>15060</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.91%</t>
+          <t>'+2.66%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>152</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>184</v>
+        <v>354</v>
       </c>
       <c r="H12" t="n">
-        <v>3.42</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13060</v>
+        <v>14670</v>
       </c>
       <c r="K12" t="n">
-        <v>13390</v>
+        <v>14800</v>
       </c>
       <c r="L12" t="n">
-        <v>13620</v>
+        <v>15270</v>
       </c>
       <c r="M12" t="n">
-        <v>12910</v>
+        <v>14800</v>
       </c>
       <c r="N12" t="n">
-        <v>3.21</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>35837174325</v>
+        <v>26358634485</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>1640</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-62000</v>
+        <v>-92000</v>
       </c>
       <c r="S12" t="n">
-        <v>-11000</v>
+        <v>7000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
+          <t>단일 판매/공급 계약 체결 공시 확인. 주가 조작 관련 언급과 함께 외인 보유율 언급. 내년 건설주 상승 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '미국장 반등']</t>
+          <t>['공시', '판매계약', '건설주']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,43 +1563,43 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>41900</v>
+        <v>13390</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.82%</t>
+          <t>'+2.53%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>229</v>
+        <v>51</v>
       </c>
       <c r="F13" t="n">
-        <v>125</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
-        <v>893</v>
+        <v>185</v>
       </c>
       <c r="H13" t="n">
-        <v>12.97</v>
+        <v>3.42</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,143 +1607,143 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>40750</v>
+        <v>13060</v>
       </c>
       <c r="K13" t="n">
-        <v>40600</v>
+        <v>13390</v>
       </c>
       <c r="L13" t="n">
-        <v>41950</v>
+        <v>13620</v>
       </c>
       <c r="M13" t="n">
-        <v>40050</v>
+        <v>12910</v>
       </c>
       <c r="N13" t="n">
-        <v>12.84</v>
+        <v>3.21</v>
       </c>
       <c r="O13" t="n">
-        <v>10501880275</v>
+        <v>36545917625</v>
       </c>
       <c r="P13" t="n">
-        <v>69200</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>24150</v>
+        <v>1640</v>
       </c>
       <c r="R13" t="n">
-        <v>15000</v>
+        <v>-62000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-11000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Class1 발표 및 FDA 승인 관련 기대감. 외인 매수세 유입 확인.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['Class1', 'FDA', '외인']</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1292000</v>
+        <v>41750</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.38%</t>
+          <t>'+2.45%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.17</v>
+        <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>230</v>
       </c>
       <c r="F14" t="n">
-        <v>514</v>
+        <v>125</v>
       </c>
       <c r="G14" t="n">
-        <v>1280</v>
+        <v>911</v>
       </c>
       <c r="H14" t="n">
-        <v>48.85</v>
+        <v>12.97</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1262000</v>
+        <v>40750</v>
       </c>
       <c r="K14" t="n">
-        <v>1290000</v>
+        <v>40600</v>
       </c>
       <c r="L14" t="n">
-        <v>1308000</v>
+        <v>41950</v>
       </c>
       <c r="M14" t="n">
-        <v>1247000</v>
+        <v>40050</v>
       </c>
       <c r="N14" t="n">
-        <v>49.02</v>
+        <v>12.84</v>
       </c>
       <c r="O14" t="n">
-        <v>3125239441500</v>
+        <v>10790127125</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>69200</v>
       </c>
       <c r="Q14" t="n">
-        <v>420500</v>
+        <v>24150</v>
       </c>
       <c r="R14" t="n">
-        <v>-448000</v>
+        <v>15000</v>
       </c>
       <c r="S14" t="n">
-        <v>-27000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 상황과 연계하여 주가 하락 우려 제기. 외인 매도 지속 및 전저점 하회 가능성 언급.</t>
+          <t>CLASS1 발표 기대감 속에 야간 선물 상승 언급. FDA 승인 관련 긍정적 해석과 함께 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외인', '주가 하락', '정치']</t>
+          <t>['CLASS1', 'FDA', '야간선물']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17860</v>
+        <v>1286000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.23%</t>
+          <t>'+1.90%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="E15" t="n">
-        <v>154</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>95</v>
+        <v>521</v>
       </c>
       <c r="G15" t="n">
-        <v>341</v>
+        <v>1335</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>48.85</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17470</v>
+        <v>1262000</v>
       </c>
       <c r="K15" t="n">
-        <v>18710</v>
+        <v>1290000</v>
       </c>
       <c r="L15" t="n">
-        <v>20300</v>
+        <v>1308000</v>
       </c>
       <c r="M15" t="n">
-        <v>17630</v>
+        <v>1247000</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>49.02</v>
       </c>
       <c r="O15" t="n">
-        <v>145153993130</v>
+        <v>3189564785500</v>
       </c>
       <c r="P15" t="n">
-        <v>28800</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>15780</v>
+        <v>420500</v>
       </c>
       <c r="R15" t="n">
-        <v>3000</v>
+        <v>-448000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-27000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>반도체 테마 및 글로벌 파운드리 연내 착공 뉴스 기반 상승 기대. 단일계좌 투주 종목으로 급락 가능성 언급.</t>
+          <t>주가 급락 및 전고점 대비 큰 하락에 대한 불만 표출. 외인 매도세 지속 및 가짜 반등 경고. 정치적 언급 다수.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['반도체', '파운드리', '단일계좌']</t>
+          <t>['주가급락', '외인매도', '가짜반등']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21000</v>
+        <v>20900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.20%</t>
+          <t>'+0.72%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2.5</v>
       </c>
       <c r="E16" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F16" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G16" t="n">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="H16" t="n">
         <v>4.28</v>
@@ -1889,7 +1889,7 @@
         <v>20500</v>
       </c>
       <c r="L16" t="n">
-        <v>21500</v>
+        <v>21550</v>
       </c>
       <c r="M16" t="n">
         <v>19440</v>
@@ -1898,7 +1898,7 @@
         <v>1.78</v>
       </c>
       <c r="O16" t="n">
-        <v>46817577320</v>
+        <v>55277841920</v>
       </c>
       <c r="P16" t="n">
         <v>22450</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>금융권 해킹 이슈 및 보안 투자 확대 뉴스 기반 신규 납품 요청 쇄도. 연기금 매수세 확인.</t>
+          <t>금융권 보안 강화 관련 뉴스 및 신규 납품 요청 소식. 연기금의 매수세와 함께 목표가 및 매수 타이밍 논의.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '신규 납품']</t>
+          <t>['보안', '납품', '연기금']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14710</v>
+        <v>14830</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.54%</t>
+          <t>'-0.74%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>68</v>
       </c>
       <c r="G17" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H17" t="n">
         <v>0.11</v>
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>39920806600</v>
+        <v>40338301950</v>
       </c>
       <c r="P17" t="n">
         <v>30800</v>
@@ -2039,27 +2039,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27000</v>
+        <v>26950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.32%</t>
+          <t>'-8.49%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F18" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G18" t="n">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="H18" t="n">
-        <v>53.41</v>
+        <v>53.4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2076,13 +2076,13 @@
         <v>29600</v>
       </c>
       <c r="M18" t="n">
-        <v>26950</v>
+        <v>26900</v>
       </c>
       <c r="N18" t="n">
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>115039405925</v>
+        <v>119013019250</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 후 주가 급락과 외국인 매도세가 관찰됩니다. 저점 매수 기회라는 의견도 있으나, 전반적으로 부정적인 전망이 우세합니다.</t>
+          <t>실적 발표 후 저점 매수 기회 언급되나, 외인 탈출 및 급락으로 인한 부정적 전망. 유투버 및 특정 세력에 대한 불신 표출.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적 발표', '외인 매도', '저점 매수']</t>
+          <t>['실적발표', '외인탈출', '저점매수']</t>
         </is>
       </c>
       <c r="X18" t="n">

--- a/data/trending_integrated_20261016_12.xlsx
+++ b/data/trending_integrated_20261016_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8610</v>
+        <v>8630</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.42%</t>
+          <t>'+20.70%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G2" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -610,7 +610,7 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>183524176735</v>
+        <v>185878661720</v>
       </c>
       <c r="P2" t="n">
         <v>8970</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>높은 상승률 기록. 인수합병 기대감 및 텐버거 가능성 언급. 거래량 증가 및 악성매물 소화 과정 설명.</t>
+          <t>인수합병 시작 기대, 4년 기다림 언급. 검은머리 외국인 향방 주목, 텐버거 가능성 언급. 거래량 증가, 악성 매물 소화 관점.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['인수합병', '텐버거', '거래량']</t>
+          <t>['인수합병', '외국인', '거래량']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7710</v>
+        <v>7780</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.35%</t>
+          <t>'+18.42%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>69457162180</v>
+        <v>70516789590</v>
       </c>
       <c r="P3" t="n">
         <v>10300</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>군공항 이전 및 호남 반도체 관련 테마 언급. 투경 종목으로 급등 가능성 및 급락 주의 신호.</t>
+          <t>군공항 이전 관련 뉴스, 신고가 돌파 8만원 가능성. 정치인 관련 언급, 시장 폭등 및 호남 관련주 주목. 종가 급락 주의, 외인 수급 변화 관찰.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['군공항', '호남 반도체', '투경']</t>
+          <t>['군공항', '호남', '외인']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8200</v>
+        <v>8150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.69%</t>
+          <t>'+13.99%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>48410343615</v>
+        <v>48829053880</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9470</v>
+        <v>9480</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.13%</t>
+          <t>'+7.24%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>83478189095</v>
+        <v>84198050220</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -931,215 +931,215 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18270</v>
+        <v>10310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.58%</t>
+          <t>'+3.83%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>155</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>346</v>
+        <v>142</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17470</v>
+        <v>9930</v>
       </c>
       <c r="K6" t="n">
-        <v>18710</v>
+        <v>10100</v>
       </c>
       <c r="L6" t="n">
-        <v>20300</v>
+        <v>11100</v>
       </c>
       <c r="M6" t="n">
-        <v>17630</v>
+        <v>9860</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>148927990820</v>
+        <v>31195707475</v>
       </c>
       <c r="P6" t="n">
-        <v>28800</v>
+        <v>19380</v>
       </c>
       <c r="Q6" t="n">
-        <v>15780</v>
+        <v>3200</v>
       </c>
       <c r="R6" t="n">
-        <v>3000</v>
+        <v>-140000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>반도체 테마 및 글로벌 파운드리 연내 착공 뉴스 기반 상승 기대. 단일계좌 투주 종목으로 급락 가능성 언급.</t>
+          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체', '파운드리', '단일계좌']</t>
+          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18960</v>
+        <v>18110</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.35%</t>
+          <t>'+3.66%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>159</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="G7" t="n">
-        <v>160</v>
+        <v>353</v>
       </c>
       <c r="H7" t="n">
-        <v>27.77</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18170</v>
+        <v>17470</v>
       </c>
       <c r="K7" t="n">
-        <v>18340</v>
+        <v>18710</v>
       </c>
       <c r="L7" t="n">
-        <v>18990</v>
+        <v>20300</v>
       </c>
       <c r="M7" t="n">
-        <v>18110</v>
+        <v>17630</v>
       </c>
       <c r="N7" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>33348139755</v>
+        <v>150768589650</v>
       </c>
       <c r="P7" t="n">
-        <v>35350</v>
+        <v>28800</v>
       </c>
       <c r="Q7" t="n">
-        <v>17210</v>
+        <v>15780</v>
       </c>
       <c r="R7" t="n">
-        <v>312000</v>
+        <v>3000</v>
       </c>
       <c r="S7" t="n">
-        <v>106000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
+          <t>반도체 테마 및 글로벌 파운드리 연내 착공 뉴스 기반 상승 기대. 단일계좌 투주 종목으로 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
+          <t>['반도체', '파운드리', '단일계좌']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>65900</v>
+        <v>18820</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.11%</t>
+          <t>'+3.58%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>409</v>
+        <v>164</v>
       </c>
       <c r="H8" t="n">
-        <v>22.1</v>
+        <v>27.77</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>63300</v>
+        <v>18170</v>
       </c>
       <c r="K8" t="n">
-        <v>63900</v>
+        <v>18340</v>
       </c>
       <c r="L8" t="n">
-        <v>66200</v>
+        <v>18990</v>
       </c>
       <c r="M8" t="n">
-        <v>63500</v>
+        <v>18110</v>
       </c>
       <c r="N8" t="n">
-        <v>22.11</v>
+        <v>27.82</v>
       </c>
       <c r="O8" t="n">
-        <v>89547543000</v>
+        <v>34679350545</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>17210</v>
       </c>
       <c r="R8" t="n">
-        <v>50000</v>
+        <v>312000</v>
       </c>
       <c r="S8" t="n">
-        <v>-24000</v>
+        <v>106000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원전 관련 긍정적 언급 및 뉴스케일파워 상승 마감 소식. 주주환원 정책 및 신뢰도에 대한 지적.</t>
+          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '뉴스케일파워', '주주환원']</t>
+          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10330</v>
+        <v>65400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.03%</t>
+          <t>'+3.32%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="G9" t="n">
-        <v>138</v>
+        <v>414</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,143 +1239,143 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9930</v>
+        <v>63300</v>
       </c>
       <c r="K9" t="n">
-        <v>10100</v>
+        <v>63900</v>
       </c>
       <c r="L9" t="n">
-        <v>11100</v>
+        <v>66200</v>
       </c>
       <c r="M9" t="n">
-        <v>9860</v>
+        <v>63500</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>22.11</v>
       </c>
       <c r="O9" t="n">
-        <v>31052767705</v>
+        <v>92758688450</v>
       </c>
       <c r="P9" t="n">
-        <v>19380</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>3200</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>-140000</v>
+        <v>50000</v>
       </c>
       <c r="S9" t="n">
-        <v>-3000</v>
+        <v>-24000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
+          <t>뉴스케일파워 상승 마감, 원전주 비교 언급. 주주 환원 정책 요구, 신뢰도 제로 지적. 3분기 매출 하회 뉴스, 신용 매도 관점.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
+          <t>['원전주', '주주환원', '매출']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>216250</v>
+        <v>21400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.98%</t>
+          <t>'+3.13%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.18</v>
+        <v>2.5</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>97</v>
       </c>
       <c r="F10" t="n">
-        <v>501</v>
+        <v>67</v>
       </c>
       <c r="G10" t="n">
-        <v>1174</v>
+        <v>238</v>
       </c>
       <c r="H10" t="n">
-        <v>45.98</v>
+        <v>4.28</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>210000</v>
+        <v>20750</v>
       </c>
       <c r="K10" t="n">
-        <v>215000</v>
+        <v>20500</v>
       </c>
       <c r="L10" t="n">
-        <v>217500</v>
+        <v>21550</v>
       </c>
       <c r="M10" t="n">
-        <v>210500</v>
+        <v>19440</v>
       </c>
       <c r="N10" t="n">
-        <v>46.16</v>
+        <v>1.78</v>
       </c>
       <c r="O10" t="n">
-        <v>1970457145250</v>
+        <v>59511896395</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>6320</v>
       </c>
       <c r="R10" t="n">
-        <v>-684000</v>
+        <v>28000</v>
       </c>
       <c r="S10" t="n">
-        <v>-108000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>이재명 정부 및 민주당 관련 부정적 언급과 함께 외인/기관 매도세 포착. 애플의 중국산 반도체 사용 검토 뉴스 언급.</t>
+          <t>농협, KDB 신규 납품 요청 및 러브콜. 금융권 보안 해킹 시도 증가 뉴스, 보안 투자 확대. 장중 조정 매수 타이밍, 오후 급등 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['역배열', '외인매도', '애플']</t>
+          <t>['보안', '납품', '투자']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,130 +1384,130 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23850</v>
+        <v>41850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.80%</t>
+          <t>'+2.70%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>232</v>
       </c>
       <c r="F11" t="n">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="G11" t="n">
-        <v>367</v>
+        <v>928</v>
       </c>
       <c r="H11" t="n">
-        <v>9.23</v>
+        <v>12.97</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>23200</v>
+        <v>40750</v>
       </c>
       <c r="K11" t="n">
-        <v>23250</v>
+        <v>40600</v>
       </c>
       <c r="L11" t="n">
-        <v>24250</v>
+        <v>41950</v>
       </c>
       <c r="M11" t="n">
-        <v>22900</v>
+        <v>40050</v>
       </c>
       <c r="N11" t="n">
-        <v>9.210000000000001</v>
+        <v>12.84</v>
       </c>
       <c r="O11" t="n">
-        <v>35619989025</v>
+        <v>11254505900</v>
       </c>
       <c r="P11" t="n">
-        <v>24950</v>
+        <v>69200</v>
       </c>
       <c r="Q11" t="n">
-        <v>17910</v>
+        <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>435000</v>
+        <v>15000</v>
       </c>
       <c r="S11" t="n">
-        <v>-20000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
+          <t>FDA 승인 관련 기대감, Class1 발표 주목. 시장 이기는 종목 없음 언급, 알바 활동 의혹 제기. 김태한 회장 신뢰 및 기다림 강조.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['운항수익', '영업이익', 'SCFI']</t>
+          <t>['FDA', 'Class1', '기대감']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15060</v>
+        <v>215000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.66%</t>
+          <t>'+2.38%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.18</v>
       </c>
       <c r="E12" t="n">
-        <v>152</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>497</v>
       </c>
       <c r="G12" t="n">
-        <v>354</v>
+        <v>1170</v>
       </c>
       <c r="H12" t="n">
-        <v>9.779999999999999</v>
+        <v>45.98</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14670</v>
+        <v>210000</v>
       </c>
       <c r="K12" t="n">
-        <v>14800</v>
+        <v>215000</v>
       </c>
       <c r="L12" t="n">
-        <v>15270</v>
+        <v>217500</v>
       </c>
       <c r="M12" t="n">
-        <v>14800</v>
+        <v>210500</v>
       </c>
       <c r="N12" t="n">
-        <v>9.710000000000001</v>
+        <v>46.16</v>
       </c>
       <c r="O12" t="n">
-        <v>26358634485</v>
+        <v>2059429468500</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R12" t="n">
-        <v>-92000</v>
+        <v>-684000</v>
       </c>
       <c r="S12" t="n">
-        <v>7000</v>
+        <v>-108000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>단일 판매/공급 계약 체결 공시 확인. 주가 조작 관련 언급과 함께 외인 보유율 언급. 내년 건설주 상승 전망.</t>
+          <t>금감원 대책 논의, 노조 성과급 vs 주주 손실, 이재명 지지율 하락 전망. JP모간 매매, 애플 중국산 반도체 사용 검토 뉴스.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공시', '판매계약', '건설주']</t>
+          <t>['금감원', '노조', '애플']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13390</v>
+        <v>23750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.53%</t>
+          <t>'+2.37%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.21</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>185</v>
+        <v>377</v>
       </c>
       <c r="H13" t="n">
-        <v>3.42</v>
+        <v>9.23</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13060</v>
+        <v>23200</v>
       </c>
       <c r="K13" t="n">
-        <v>13390</v>
+        <v>23250</v>
       </c>
       <c r="L13" t="n">
-        <v>13620</v>
+        <v>24250</v>
       </c>
       <c r="M13" t="n">
-        <v>12910</v>
+        <v>22900</v>
       </c>
       <c r="N13" t="n">
-        <v>3.21</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>36545917625</v>
+        <v>36456631975</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>24950</v>
       </c>
       <c r="Q13" t="n">
-        <v>1640</v>
+        <v>17910</v>
       </c>
       <c r="R13" t="n">
-        <v>-62000</v>
+        <v>435000</v>
       </c>
       <c r="S13" t="n">
-        <v>-11000</v>
+        <v>-20000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
+          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '미국장 반등']</t>
+          <t>['운항수익', '영업이익', 'SCFI']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>011200</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>41750</v>
+        <v>14970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.45%</t>
+          <t>'+2.04%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="F14" t="n">
-        <v>125</v>
+        <v>46</v>
       </c>
       <c r="G14" t="n">
-        <v>911</v>
+        <v>372</v>
       </c>
       <c r="H14" t="n">
-        <v>12.97</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>40750</v>
+        <v>14670</v>
       </c>
       <c r="K14" t="n">
-        <v>40600</v>
+        <v>14800</v>
       </c>
       <c r="L14" t="n">
-        <v>41950</v>
+        <v>15270</v>
       </c>
       <c r="M14" t="n">
-        <v>40050</v>
+        <v>14800</v>
       </c>
       <c r="N14" t="n">
-        <v>12.84</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>10790127125</v>
+        <v>27291217885</v>
       </c>
       <c r="P14" t="n">
-        <v>69200</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>24150</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>15000</v>
+        <v>-92000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>CLASS1 발표 기대감 속에 야간 선물 상승 언급. FDA 승인 관련 긍정적 해석과 함께 주가 상승 전망.</t>
+          <t>대우건설 단일판매 공시, 내년 건설주 상승 전망. 금감원 사모펀드 긴급 점검, 주가 조작 관련 언급. 주주 대차 해지 중요성 강조.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['CLASS1', 'FDA', '야간선물']</t>
+          <t>['공시', '건설주', '사모펀드']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,86 +1752,86 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1286000</v>
+        <v>13280</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.90%</t>
+          <t>'+1.68%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>52</v>
       </c>
       <c r="F15" t="n">
-        <v>521</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>1335</v>
+        <v>186</v>
       </c>
       <c r="H15" t="n">
-        <v>48.85</v>
+        <v>3.42</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1262000</v>
+        <v>13060</v>
       </c>
       <c r="K15" t="n">
-        <v>1290000</v>
+        <v>13390</v>
       </c>
       <c r="L15" t="n">
-        <v>1308000</v>
+        <v>13620</v>
       </c>
       <c r="M15" t="n">
-        <v>1247000</v>
+        <v>12910</v>
       </c>
       <c r="N15" t="n">
-        <v>49.02</v>
+        <v>3.21</v>
       </c>
       <c r="O15" t="n">
-        <v>3189564785500</v>
+        <v>37679324700</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q15" t="n">
-        <v>420500</v>
+        <v>1640</v>
       </c>
       <c r="R15" t="n">
-        <v>-448000</v>
+        <v>-62000</v>
       </c>
       <c r="S15" t="n">
-        <v>-27000</v>
+        <v>-11000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 급락 및 전고점 대비 큰 하락에 대한 불만 표출. 외인 매도세 지속 및 가짜 반등 경고. 정치적 언급 다수.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가급락', '외인매도', '가짜반등']</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,95 +1839,95 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20900</v>
+        <v>1275500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.72%</t>
+          <t>'+1.07%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2.5</v>
+        <v>-0.17</v>
       </c>
       <c r="E16" t="n">
-        <v>91</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>63</v>
+        <v>520</v>
       </c>
       <c r="G16" t="n">
-        <v>227</v>
+        <v>1405</v>
       </c>
       <c r="H16" t="n">
-        <v>4.28</v>
+        <v>48.85</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>20750</v>
+        <v>1262000</v>
       </c>
       <c r="K16" t="n">
-        <v>20500</v>
+        <v>1290000</v>
       </c>
       <c r="L16" t="n">
-        <v>21550</v>
+        <v>1308000</v>
       </c>
       <c r="M16" t="n">
-        <v>19440</v>
+        <v>1247000</v>
       </c>
       <c r="N16" t="n">
-        <v>1.78</v>
+        <v>49.02</v>
       </c>
       <c r="O16" t="n">
-        <v>55277841920</v>
+        <v>3288619525000</v>
       </c>
       <c r="P16" t="n">
-        <v>22450</v>
+        <v>2987000</v>
       </c>
       <c r="Q16" t="n">
-        <v>6320</v>
+        <v>420500</v>
       </c>
       <c r="R16" t="n">
-        <v>28000</v>
+        <v>-448000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-27000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>금융권 보안 강화 관련 뉴스 및 신규 납품 요청 소식. 연기금의 매수세와 함께 목표가 및 매수 타이밍 논의.</t>
+          <t>주가 하락 및 반응 없음 지적, 최태원 주주 피눈물 호소. 정치 성향 무관 외인 매도 지속, 전저점 돌파 시 하락 전망. 솔리다임 상장 이슈.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['보안', '납품', '연기금']</t>
+          <t>['주가관리', '외인', '솔리다임']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14830</v>
+        <v>14790</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.74%</t>
+          <t>'-1.00%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>161</v>
       </c>
       <c r="F17" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G17" t="n">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="H17" t="n">
         <v>0.11</v>
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>40338301950</v>
+        <v>40605486320</v>
       </c>
       <c r="P17" t="n">
         <v>30800</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>상장 사기 및 지나치게 높은 공모가에 대한 강한 비판이 제기됨. 회사 경영진의 무능함과 자진 상폐 요구가 포함됨.</t>
+          <t>상장 사기, 피해자 발생 언급. 김임준 대표 사퇴 요구, 공모가 및 시총 과대 지적. 자사주 매입 및 자진 상폐 요구.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['상장 사기', '공모가', '자진 상폐']</t>
+          <t>['상장사기', '공모가', '자진상폐']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,27 +2039,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26950</v>
+        <v>26850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.49%</t>
+          <t>'-8.83%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G18" t="n">
-        <v>360</v>
+        <v>387</v>
       </c>
       <c r="H18" t="n">
-        <v>53.4</v>
+        <v>53.39</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2076,13 +2076,13 @@
         <v>29600</v>
       </c>
       <c r="M18" t="n">
-        <v>26900</v>
+        <v>26800</v>
       </c>
       <c r="N18" t="n">
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>119013019250</v>
+        <v>124600368400</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 후 저점 매수 기회 언급되나, 외인 탈출 및 급락으로 인한 부정적 전망. 유투버 및 특정 세력에 대한 불신 표출.</t>
+          <t>실적 발표 후 배당, 저점 매수 기회 언급. 외인 탈출 시작, 유튜버 및 신한 증권 신뢰 불가 의견. 실적 호조에도 폭락, 갑작스러운 매도.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적발표', '외인탈출', '저점매수']</t>
+          <t>['실적', '배당', '외인']</t>
         </is>
       </c>
       <c r="X18" t="n">

--- a/data/trending_integrated_20261016_12.xlsx
+++ b/data/trending_integrated_20261016_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8630</v>
+        <v>8560</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.70%</t>
+          <t>'+19.72%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F2" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G2" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -610,7 +610,7 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>185878661720</v>
+        <v>187719201995</v>
       </c>
       <c r="P2" t="n">
         <v>8970</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7780</v>
+        <v>7820</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.42%</t>
+          <t>'+19.03%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3" t="n">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>70516789590</v>
+        <v>70845061315</v>
       </c>
       <c r="P3" t="n">
         <v>10300</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>군공항 이전 관련 뉴스, 신고가 돌파 8만원 가능성. 정치인 관련 언급, 시장 폭등 및 호남 관련주 주목. 종가 급락 주의, 외인 수급 변화 관찰.</t>
+          <t>군공항 이전 관련 이슈 언급 및 신고가 돌파 기대감 표출. 정치권 언급 및 외인 동향 주시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['군공항', '호남', '외인']</t>
+          <t>['군공항', '신고가', '외인']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8150</v>
+        <v>8180</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.99%</t>
+          <t>'+14.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
         <v>231</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>48829053880</v>
+        <v>49110419510</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9480</v>
+        <v>9400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.24%</t>
+          <t>'+6.33%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
         <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>84198050220</v>
+        <v>84630877210</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10310</v>
+        <v>10370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.83%</t>
+          <t>'+4.43%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
         <v>142</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>31195707475</v>
+        <v>31337213620</v>
       </c>
       <c r="P6" t="n">
         <v>19380</v>
@@ -1023,123 +1023,123 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>18950</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'+4.29%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E7" t="n">
+        <v>49</v>
+      </c>
+      <c r="F7" t="n">
+        <v>33</v>
+      </c>
+      <c r="G7" t="n">
+        <v>165</v>
+      </c>
+      <c r="H7" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>18170</v>
+      </c>
+      <c r="K7" t="n">
+        <v>18340</v>
+      </c>
+      <c r="L7" t="n">
+        <v>18990</v>
+      </c>
+      <c r="M7" t="n">
         <v>18110</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>'+3.66%</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>159</v>
-      </c>
-      <c r="F7" t="n">
-        <v>96</v>
-      </c>
-      <c r="G7" t="n">
-        <v>353</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>17470</v>
-      </c>
-      <c r="K7" t="n">
-        <v>18710</v>
-      </c>
-      <c r="L7" t="n">
-        <v>20300</v>
-      </c>
-      <c r="M7" t="n">
-        <v>17630</v>
-      </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>27.82</v>
       </c>
       <c r="O7" t="n">
-        <v>150768589650</v>
+        <v>36108450070</v>
       </c>
       <c r="P7" t="n">
-        <v>28800</v>
+        <v>35350</v>
       </c>
       <c r="Q7" t="n">
-        <v>15780</v>
+        <v>17210</v>
       </c>
       <c r="R7" t="n">
-        <v>3000</v>
+        <v>312000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>106000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>반도체 테마 및 글로벌 파운드리 연내 착공 뉴스 기반 상승 기대. 단일계좌 투주 종목으로 급락 가능성 언급.</t>
+          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반도체', '파운드리', '단일계좌']</t>
+          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18820</v>
+        <v>66000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.58%</t>
+          <t>'+4.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="G8" t="n">
-        <v>164</v>
+        <v>424</v>
       </c>
       <c r="H8" t="n">
-        <v>27.77</v>
+        <v>22.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18170</v>
+        <v>63300</v>
       </c>
       <c r="K8" t="n">
-        <v>18340</v>
+        <v>63900</v>
       </c>
       <c r="L8" t="n">
-        <v>18990</v>
+        <v>66200</v>
       </c>
       <c r="M8" t="n">
-        <v>18110</v>
+        <v>63500</v>
       </c>
       <c r="N8" t="n">
-        <v>27.82</v>
+        <v>22.11</v>
       </c>
       <c r="O8" t="n">
-        <v>34679350545</v>
+        <v>95346135050</v>
       </c>
       <c r="P8" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>17210</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>312000</v>
+        <v>50000</v>
       </c>
       <c r="S8" t="n">
-        <v>106000</v>
+        <v>-24000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
+          <t>뉴스케일파워 등 원전 관련 섹터 상승세 언급. 3분기 매출 하회 소식 및 주주 환원 정책 촉구.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
+          <t>['원전', '매출', '주주환원']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65400</v>
+        <v>218500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.32%</t>
+          <t>'+4.05%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>-0.18</v>
       </c>
       <c r="E9" t="n">
-        <v>136</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="G9" t="n">
-        <v>414</v>
+        <v>1181</v>
       </c>
       <c r="H9" t="n">
-        <v>22.1</v>
+        <v>45.98</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>63300</v>
+        <v>210000</v>
       </c>
       <c r="K9" t="n">
-        <v>63900</v>
+        <v>215000</v>
       </c>
       <c r="L9" t="n">
-        <v>66200</v>
+        <v>218500</v>
       </c>
       <c r="M9" t="n">
-        <v>63500</v>
+        <v>210500</v>
       </c>
       <c r="N9" t="n">
-        <v>22.11</v>
+        <v>46.16</v>
       </c>
       <c r="O9" t="n">
-        <v>92758688450</v>
+        <v>2192672991000</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>50000</v>
+        <v>-684000</v>
       </c>
       <c r="S9" t="n">
-        <v>-24000</v>
+        <v>-108000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>뉴스케일파워 상승 마감, 원전주 비교 언급. 주주 환원 정책 요구, 신뢰도 제로 지적. 3분기 매출 하회 뉴스, 신용 매도 관점.</t>
+          <t>이재명 대표 관련 정치적 이슈 언급 및 미국 CNBC 뉴스, JP모건 수급 분석. 25만/30만 돌파 기대감 표출.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전주', '주주환원', '매출']</t>
+          <t>['정치', '수급', '뉴스']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21400</v>
+        <v>18160</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.13%</t>
+          <t>'+3.95%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="F10" t="n">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>238</v>
+        <v>373</v>
       </c>
       <c r="H10" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>20750</v>
+        <v>17470</v>
       </c>
       <c r="K10" t="n">
-        <v>20500</v>
+        <v>18710</v>
       </c>
       <c r="L10" t="n">
-        <v>21550</v>
+        <v>20300</v>
       </c>
       <c r="M10" t="n">
-        <v>19440</v>
+        <v>17630</v>
       </c>
       <c r="N10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>59511896395</v>
+        <v>151860749075</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>28800</v>
       </c>
       <c r="Q10" t="n">
-        <v>6320</v>
+        <v>15780</v>
       </c>
       <c r="R10" t="n">
-        <v>28000</v>
+        <v>3000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>농협, KDB 신규 납품 요청 및 러브콜. 금융권 보안 해킹 시도 증가 뉴스, 보안 투자 확대. 장중 조정 매수 타이밍, 오후 급등 기대.</t>
+          <t>반도체 테마 관련주로 일본/호남 반도체 공장 수혜 기대. 글로벌 파운드리 연내 착공 속보 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안', '납품', '투자']</t>
+          <t>['반도체', '수혜', '파운드리']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>41850</v>
+        <v>42300</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.70%</t>
+          <t>'+3.80%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.13</v>
       </c>
       <c r="E11" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F11" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G11" t="n">
-        <v>928</v>
+        <v>956</v>
       </c>
       <c r="H11" t="n">
         <v>12.97</v>
@@ -1429,7 +1429,7 @@
         <v>40600</v>
       </c>
       <c r="L11" t="n">
-        <v>41950</v>
+        <v>42300</v>
       </c>
       <c r="M11" t="n">
         <v>40050</v>
@@ -1438,7 +1438,7 @@
         <v>12.84</v>
       </c>
       <c r="O11" t="n">
-        <v>11254505900</v>
+        <v>12171380250</v>
       </c>
       <c r="P11" t="n">
         <v>69200</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>FDA 승인 관련 기대감, Class1 발표 주목. 시장 이기는 종목 없음 언급, 알바 활동 의혹 제기. 김태한 회장 신뢰 및 기다림 강조.</t>
+          <t>Class1 발표 임박 기대감 및 FDA 승인 가능성 언급. 진양곤 회장 IR 활동 및 주가 흐름 주시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['FDA', 'Class1', '기대감']</t>
+          <t>['FDA', 'Class1', 'IR']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,79 +1483,79 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>215000</v>
+        <v>13450</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.38%</t>
+          <t>'+2.99%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.18</v>
+        <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>497</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>1170</v>
+        <v>193</v>
       </c>
       <c r="H12" t="n">
-        <v>45.98</v>
+        <v>3.42</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>210000</v>
+        <v>13060</v>
       </c>
       <c r="K12" t="n">
-        <v>215000</v>
+        <v>13390</v>
       </c>
       <c r="L12" t="n">
-        <v>217500</v>
+        <v>13620</v>
       </c>
       <c r="M12" t="n">
-        <v>210500</v>
+        <v>12910</v>
       </c>
       <c r="N12" t="n">
-        <v>46.16</v>
+        <v>3.21</v>
       </c>
       <c r="O12" t="n">
-        <v>2059429468500</v>
+        <v>38377375310</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>94500</v>
+        <v>1640</v>
       </c>
       <c r="R12" t="n">
-        <v>-684000</v>
+        <v>-62000</v>
       </c>
       <c r="S12" t="n">
-        <v>-108000</v>
+        <v>-11000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>금감원 대책 논의, 노조 성과급 vs 주주 손실, 이재명 지지율 하락 전망. JP모간 매매, 애플 중국산 반도체 사용 검토 뉴스.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['금감원', '노조', '애플']</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,43 +1563,43 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23750</v>
+        <v>1299000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.37%</t>
+          <t>'+2.93%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>-0.17</v>
       </c>
       <c r="E13" t="n">
-        <v>62</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>511</v>
       </c>
       <c r="G13" t="n">
-        <v>377</v>
+        <v>1390</v>
       </c>
       <c r="H13" t="n">
-        <v>9.23</v>
+        <v>48.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,60 +1607,60 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>23200</v>
+        <v>1262000</v>
       </c>
       <c r="K13" t="n">
-        <v>23250</v>
+        <v>1290000</v>
       </c>
       <c r="L13" t="n">
-        <v>24250</v>
+        <v>1308000</v>
       </c>
       <c r="M13" t="n">
-        <v>22900</v>
+        <v>1247000</v>
       </c>
       <c r="N13" t="n">
-        <v>9.210000000000001</v>
+        <v>49.02</v>
       </c>
       <c r="O13" t="n">
-        <v>36456631975</v>
+        <v>3404408341000</v>
       </c>
       <c r="P13" t="n">
-        <v>24950</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>17910</v>
+        <v>420500</v>
       </c>
       <c r="R13" t="n">
-        <v>435000</v>
+        <v>-448000</v>
       </c>
       <c r="S13" t="n">
-        <v>-20000</v>
+        <v>-27000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
+          <t>최태원 회장 경영 비판 및 주가 관리 촉구. 외인 매도 지속 및 솔리다임 상장 이슈 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['운항수익', '영업이익', 'SCFI']</t>
+          <t>['경영', '외인', '이슈']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14970</v>
+        <v>15090</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.04%</t>
+          <t>'+2.86%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="H14" t="n">
         <v>9.779999999999999</v>
@@ -1714,7 +1714,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>27291217885</v>
+        <v>27826862560</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13280</v>
+        <v>15320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.68%</t>
+          <t>'+2.54%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>52</v>
+        <v>166</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="G15" t="n">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="H15" t="n">
-        <v>3.42</v>
+        <v>0.11</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>13060</v>
+        <v>14940</v>
       </c>
       <c r="K15" t="n">
-        <v>13390</v>
+        <v>14940</v>
       </c>
       <c r="L15" t="n">
-        <v>13620</v>
+        <v>16290</v>
       </c>
       <c r="M15" t="n">
-        <v>12910</v>
+        <v>14330</v>
       </c>
       <c r="N15" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>37679324700</v>
+        <v>43423795160</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>30800</v>
       </c>
       <c r="Q15" t="n">
-        <v>1640</v>
+        <v>9810</v>
       </c>
       <c r="R15" t="n">
-        <v>-62000</v>
+        <v>7000</v>
       </c>
       <c r="S15" t="n">
-        <v>-11000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
+          <t>상장 사기, 피해자 발생 언급. 김임준 대표 사퇴 요구, 공모가 및 시총 과대 지적. 자사주 매입 및 자진 상폐 요구.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '미국장 반등']</t>
+          <t>['상장사기', '공모가', '자진상폐']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1275500</v>
+        <v>23750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.07%</t>
+          <t>'+2.37%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.17</v>
+        <v>0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>64</v>
       </c>
       <c r="F16" t="n">
-        <v>520</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>1405</v>
+        <v>383</v>
       </c>
       <c r="H16" t="n">
-        <v>48.85</v>
+        <v>9.23</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1262000</v>
+        <v>23200</v>
       </c>
       <c r="K16" t="n">
-        <v>1290000</v>
+        <v>23250</v>
       </c>
       <c r="L16" t="n">
-        <v>1308000</v>
+        <v>24250</v>
       </c>
       <c r="M16" t="n">
-        <v>1247000</v>
+        <v>22900</v>
       </c>
       <c r="N16" t="n">
-        <v>49.02</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>3288619525000</v>
+        <v>37365765775</v>
       </c>
       <c r="P16" t="n">
-        <v>2987000</v>
+        <v>24950</v>
       </c>
       <c r="Q16" t="n">
-        <v>420500</v>
+        <v>17910</v>
       </c>
       <c r="R16" t="n">
-        <v>-448000</v>
+        <v>435000</v>
       </c>
       <c r="S16" t="n">
-        <v>-27000</v>
+        <v>-20000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 하락 및 반응 없음 지적, 최태원 주주 피눈물 호소. 정치 성향 무관 외인 매도 지속, 전저점 돌파 시 하락 전망. 솔리다임 상장 이슈.</t>
+          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가관리', '외인', '솔리다임']</t>
+          <t>['운항수익', '영업이익', 'SCFI']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>011200</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14790</v>
+        <v>21100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.00%</t>
+          <t>'+1.69%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="E17" t="n">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="F17" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G17" t="n">
-        <v>208</v>
+        <v>258</v>
       </c>
       <c r="H17" t="n">
-        <v>0.11</v>
+        <v>4.28</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>14940</v>
+        <v>20750</v>
       </c>
       <c r="K17" t="n">
-        <v>14940</v>
+        <v>20500</v>
       </c>
       <c r="L17" t="n">
-        <v>16290</v>
+        <v>21550</v>
       </c>
       <c r="M17" t="n">
-        <v>14330</v>
+        <v>19440</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O17" t="n">
-        <v>40605486320</v>
+        <v>62420611245</v>
       </c>
       <c r="P17" t="n">
-        <v>30800</v>
+        <v>22450</v>
       </c>
       <c r="Q17" t="n">
-        <v>9810</v>
+        <v>6320</v>
       </c>
       <c r="R17" t="n">
-        <v>7000</v>
+        <v>28000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>상장 사기, 피해자 발생 언급. 김임준 대표 사퇴 요구, 공모가 및 시총 과대 지적. 자사주 매입 및 자진 상폐 요구.</t>
+          <t>농협, KDB 등 신규 납품 요청 및 보안 투자 확대 뉴스 기반 상승 기대. 양자보안 관련 내용 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['상장사기', '공모가', '자진상폐']</t>
+          <t>['보안', '납품', '투자']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26850</v>
+        <v>26900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.83%</t>
+          <t>'-8.66%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F18" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G18" t="n">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="H18" t="n">
         <v>53.39</v>
@@ -2076,13 +2076,13 @@
         <v>29600</v>
       </c>
       <c r="M18" t="n">
-        <v>26800</v>
+        <v>26750</v>
       </c>
       <c r="N18" t="n">
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>124600368400</v>
+        <v>129241295500</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 후 배당, 저점 매수 기회 언급. 외인 탈출 시작, 유튜버 및 신한 증권 신뢰 불가 의견. 실적 호조에도 폭락, 갑작스러운 매도.</t>
+          <t>실적 발표 후 저점 매수 기회 언급. 외인 프로그램 매도 및 일봉 차트 붕괴 우려 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적', '배당', '외인']</t>
+          <t>['실적', '외인', '매수']</t>
         </is>
       </c>
       <c r="X18" t="n">
